--- a/March_Release_SCB/Cypress/fixtures/AgencyTemplate.xlsx
+++ b/March_Release_SCB/Cypress/fixtures/AgencyTemplate.xlsx
@@ -466,10 +466,10 @@
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>17657</v>
+        <v>250617</v>
       </c>
       <c r="D2" t="str">
-        <v>WikiLTDPma</v>
+        <v>Kayden</v>
       </c>
       <c r="E2" t="str">
         <v>2256</v>
@@ -484,7 +484,7 @@
         <v>12345321</v>
       </c>
       <c r="I2" t="str">
-        <v>BOOPS9614B</v>
+        <v>PANCA9614B</v>
       </c>
       <c r="J2" t="str">
         <v>hamad</v>
@@ -499,10 +499,10 @@
         <v>wiki field</v>
       </c>
       <c r="N2" t="str">
-        <v>9960072202</v>
+        <v>2588784715</v>
       </c>
       <c r="O2" t="str">
-        <v>hamad0679@yopmail.com</v>
+        <v>kayden@yopmail.com</v>
       </c>
       <c r="P2" t="str">
         <v>12-10-2022</v>

--- a/March_Release_SCB/Cypress/fixtures/AgencyTemplate.xlsx
+++ b/March_Release_SCB/Cypress/fixtures/AgencyTemplate.xlsx
@@ -466,10 +466,10 @@
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>250617</v>
+        <v>626040</v>
       </c>
       <c r="D2" t="str">
-        <v>Kayden</v>
+        <v>Pearl</v>
       </c>
       <c r="E2" t="str">
         <v>2256</v>
@@ -499,10 +499,10 @@
         <v>wiki field</v>
       </c>
       <c r="N2" t="str">
-        <v>2588784715</v>
+        <v>8748511337</v>
       </c>
       <c r="O2" t="str">
-        <v>kayden@yopmail.com</v>
+        <v>pearl@yopmail.com</v>
       </c>
       <c r="P2" t="str">
         <v>12-10-2022</v>
@@ -514,7 +514,7 @@
         <v>10-10-2032</v>
       </c>
       <c r="S2" t="str">
-        <v>Bulk upl$%56oad</v>
+        <v>Bulk upload</v>
       </c>
     </row>
   </sheetData>

--- a/March_Release_SCB/Cypress/fixtures/AgencyTemplate.xlsx
+++ b/March_Release_SCB/Cypress/fixtures/AgencyTemplate.xlsx
@@ -466,10 +466,10 @@
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>626040</v>
+        <v>701863</v>
       </c>
       <c r="D2" t="str">
-        <v>Pearl</v>
+        <v>Janiya</v>
       </c>
       <c r="E2" t="str">
         <v>2256</v>
@@ -499,10 +499,10 @@
         <v>wiki field</v>
       </c>
       <c r="N2" t="str">
-        <v>8748511337</v>
+        <v>1477435206</v>
       </c>
       <c r="O2" t="str">
-        <v>pearl@yopmail.com</v>
+        <v>janiya@yopmail.com</v>
       </c>
       <c r="P2" t="str">
         <v>12-10-2022</v>
@@ -514,7 +514,7 @@
         <v>10-10-2032</v>
       </c>
       <c r="S2" t="str">
-        <v>Bulk upload</v>
+        <v>Bulk upl$%56oad</v>
       </c>
     </row>
   </sheetData>

--- a/March_Release_SCB/Cypress/fixtures/AgencyTemplate.xlsx
+++ b/March_Release_SCB/Cypress/fixtures/AgencyTemplate.xlsx
@@ -466,10 +466,10 @@
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>701863</v>
+        <v>504460</v>
       </c>
       <c r="D2" t="str">
-        <v>Janiya</v>
+        <v>Shirley</v>
       </c>
       <c r="E2" t="str">
         <v>2256</v>
@@ -499,10 +499,10 @@
         <v>wiki field</v>
       </c>
       <c r="N2" t="str">
-        <v>1477435206</v>
+        <v>7411683181</v>
       </c>
       <c r="O2" t="str">
-        <v>janiya@yopmail.com</v>
+        <v>shirley@yopmail.com</v>
       </c>
       <c r="P2" t="str">
         <v>12-10-2022</v>
@@ -514,7 +514,7 @@
         <v>10-10-2032</v>
       </c>
       <c r="S2" t="str">
-        <v>Bulk upl$%56oad</v>
+        <v>Bulk up56oad</v>
       </c>
     </row>
   </sheetData>

--- a/March_Release_SCB/Cypress/fixtures/AgencyTemplate.xlsx
+++ b/March_Release_SCB/Cypress/fixtures/AgencyTemplate.xlsx
@@ -466,10 +466,10 @@
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>504460</v>
+        <v>928783</v>
       </c>
       <c r="D2" t="str">
-        <v>Shirley</v>
+        <v>Evangeline</v>
       </c>
       <c r="E2" t="str">
         <v>2256</v>
@@ -499,10 +499,10 @@
         <v>wiki field</v>
       </c>
       <c r="N2" t="str">
-        <v>7411683181</v>
+        <v/>
       </c>
       <c r="O2" t="str">
-        <v>shirley@yopmail.com</v>
+        <v>evangeline@yopmail.com</v>
       </c>
       <c r="P2" t="str">
         <v>12-10-2022</v>
@@ -514,7 +514,7 @@
         <v>10-10-2032</v>
       </c>
       <c r="S2" t="str">
-        <v>Bulk up56oad</v>
+        <v>Bulk upload</v>
       </c>
     </row>
   </sheetData>

--- a/March_Release_SCB/Cypress/fixtures/AgencyTemplate.xlsx
+++ b/March_Release_SCB/Cypress/fixtures/AgencyTemplate.xlsx
@@ -466,10 +466,10 @@
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>928783</v>
+        <v>757375</v>
       </c>
       <c r="D2" t="str">
-        <v>Evangeline</v>
+        <v>Natalie</v>
       </c>
       <c r="E2" t="str">
         <v>2256</v>
@@ -499,10 +499,10 @@
         <v>wiki field</v>
       </c>
       <c r="N2" t="str">
-        <v/>
+        <v>4722119024</v>
       </c>
       <c r="O2" t="str">
-        <v>evangeline@yopmail.com</v>
+        <v>natalie@yopmail.com</v>
       </c>
       <c r="P2" t="str">
         <v>12-10-2022</v>
@@ -514,7 +514,7 @@
         <v>10-10-2032</v>
       </c>
       <c r="S2" t="str">
-        <v>Bulk upload</v>
+        <v>Bulk up56oad</v>
       </c>
     </row>
   </sheetData>
